--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\WI\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18DCB2CF-79EA-41BC-AD90-DF7B2A00EABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D91BE42-066A-48C4-BA2F-0A27BDD127FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10865" windowHeight="10080" firstSheet="1" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
+    <workbookView xWindow="520" yWindow="520" windowWidth="14480" windowHeight="10080" firstSheet="1" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -604,9 +604,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667665C7-8A8E-46D9-B686-64BA7741F669}">
   <dimension ref="A1:C43"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -614,20 +614,20 @@
         <v>63</v>
       </c>
       <c r="C1" s="3">
-        <v>45238</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -635,147 +635,147 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>62</v>
       </c>
@@ -792,12 +792,12 @@
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.54296875" customWidth="1"/>
+    <col min="1" max="1" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -805,7 +805,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -813,7 +813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -821,7 +821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -829,7 +829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -837,7 +837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -845,7 +845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -853,7 +853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -861,7 +861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -869,7 +869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -877,7 +877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -885,7 +885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -893,7 +893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -901,7 +901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -909,7 +909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -917,7 +917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -925,7 +925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -933,7 +933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -941,7 +941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -949,7 +949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -957,7 +957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -965,7 +965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -973,7 +973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -989,7 +989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -1008,13 +1008,13 @@
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.54296875" customWidth="1"/>
-    <col min="2" max="2" width="19.1328125" customWidth="1"/>
+    <col min="1" max="1" width="34.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -1041,9 +1041,9 @@
     <tabColor theme="4" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>49</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1083,7 +1083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>47</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>48</v>
       </c>

--- a/InputData/elec/RAF/Regional Availability Factor.xlsx
+++ b/InputData/elec/RAF/Regional Availability Factor.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\WI\elec\RAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9D91BE42-066A-48C4-BA2F-0A27BDD127FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{711912B4-C551-4BB9-B912-3EEF947AC703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="520" yWindow="520" windowWidth="14480" windowHeight="10080" firstSheet="1" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
+    <workbookView xWindow="810" yWindow="660" windowWidth="15870" windowHeight="16425" activeTab="1" xr2:uid="{D718C537-5235-45E1-A117-07B097D2BDF0}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="RAF-generation" sheetId="2" r:id="rId2"/>
-    <sheet name="RAF-demand-altering-techs" sheetId="3" r:id="rId3"/>
-    <sheet name="RAF-capacity" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="RAF-generation" sheetId="2" r:id="rId3"/>
+    <sheet name="RAF-demand-altering-techs" sheetId="3" r:id="rId4"/>
+    <sheet name="RAF-capacity" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="161">
   <si>
     <t>Source:</t>
   </si>
@@ -230,14 +231,305 @@
     <t>for the electricity sector.</t>
   </si>
   <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>Connecticut</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Idaho</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>KS</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>KY</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>LA</t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>ME</t>
+  </si>
+  <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>Missouri</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Mississippi</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>ND</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>NJ</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>NM</t>
+  </si>
+  <si>
+    <t>New Mexico</t>
+  </si>
+  <si>
+    <t>NV</t>
+  </si>
+  <si>
+    <t>Nevada</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>OH</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Oklahoma</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>RI</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
+  </si>
+  <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>UT</t>
+  </si>
+  <si>
+    <t>Utah</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>VT</t>
+  </si>
+  <si>
+    <t>Vermont</t>
+  </si>
+  <si>
+    <t>WA</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
     <t>Wisconsin</t>
+  </si>
+  <si>
+    <t>WV</t>
+  </si>
+  <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
+    <t>WY</t>
+  </si>
+  <si>
+    <t>Wyoming</t>
+  </si>
+  <si>
+    <t>custom hydro values</t>
+  </si>
+  <si>
+    <t>custom coal values</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,13 +553,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -282,13 +588,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -603,181 +911,503 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667665C7-8A8E-46D9-B686-64BA7741F669}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="C1" s="3">
-        <v>45294</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45345</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="str">
+        <f>INDEX($F$1:$F$48,MATCH(B1,G1:G48,0))</f>
+        <v>WI</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F10" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="F15" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F17" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F18" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F19" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F20" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F21" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F22" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F23" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F24" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F25" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F26" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G26" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F27" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F28" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F29" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F30" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F31" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F32" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G32" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F33" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G33" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F34" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G34" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F35" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G35" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F37" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G37" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F38" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G38" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F39" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G39" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F40" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G40" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F41" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G41" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F42" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G42" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>62</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F44" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G44" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F45" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G45" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F46" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G46" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F47" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G47" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F48" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G48" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -787,6 +1417,699 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA50FD77-C708-45C5-9CA6-A7E0CC8C4090}">
+  <dimension ref="B1:E49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C35" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" t="s">
+        <v>132</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C39" t="s">
+        <v>138</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B41" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C41" t="s">
+        <v>142</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B42" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C42" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B43" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C43" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B44" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C44" t="s">
+        <v>148</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" s="5">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B45" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" t="s">
+        <v>150</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B46" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C46" t="s">
+        <v>152</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B47" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" t="s">
+        <v>154</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B48" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C48" t="s">
+        <v>156</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C49" t="s">
+        <v>158</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5D9ED82-0D6D-4554-A249-670AA724E405}">
   <sheetPr>
     <tabColor theme="4" tint="-0.499984740745262"/>
@@ -810,6 +2133,7 @@
         <v>2</v>
       </c>
       <c r="B2">
+        <f>INDEX(Sheet1!E:E,MATCH(About!B2,Sheet1!B:B,0))</f>
         <v>1</v>
       </c>
     </row>
@@ -842,6 +2166,7 @@
         <v>6</v>
       </c>
       <c r="B6">
+        <f>INDEX(Sheet1!$D$2:$D$49,MATCH(About!B1,Sheet1!$C$2:$C$49,0))</f>
         <v>1</v>
       </c>
     </row>
@@ -1002,7 +2327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF6E62-1D44-4071-9B4B-8D8AD9AB16B0}">
   <sheetPr>
     <tabColor theme="4" tint="-0.499984740745262"/>
@@ -1035,7 +2360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED7E3B8-DB01-4BFB-908D-32A466D537CF}">
   <sheetPr>
     <tabColor theme="4" tint="-0.499984740745262"/>
